--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515677</v>
+        <v>118515676</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585717</v>
+        <v>585719</v>
       </c>
       <c r="R6" t="n">
-        <v>7060027</v>
+        <v>7060029</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515676</v>
+        <v>118515695</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585719</v>
+        <v>585636</v>
       </c>
       <c r="R7" t="n">
-        <v>7060029</v>
+        <v>7060036</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118515673</v>
+        <v>118515696</v>
       </c>
       <c r="B8" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,46 +1363,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585723</v>
+        <v>585601</v>
       </c>
       <c r="R8" t="n">
-        <v>7060030</v>
+        <v>7060135</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1461,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118515692</v>
+        <v>118515671</v>
       </c>
       <c r="B9" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,34 +1470,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585656</v>
+        <v>585724</v>
       </c>
       <c r="R9" t="n">
-        <v>7060035</v>
+        <v>7060051</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1563,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118515694</v>
+        <v>118515692</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,42 +1577,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585649</v>
+        <v>585656</v>
       </c>
       <c r="R10" t="n">
-        <v>7060032</v>
+        <v>7060035</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1647,11 +1637,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färskt bohål, 20 cm djupt, 5cm i diameter, 1,5m ovan  mark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118515669</v>
+        <v>118515681</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,34 +1679,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585726</v>
+        <v>585705</v>
       </c>
       <c r="R11" t="n">
-        <v>7060027</v>
+        <v>7060019</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1780,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515681</v>
+        <v>118515693</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1816,7 +1806,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1825,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585705</v>
+        <v>585653</v>
       </c>
       <c r="R12" t="n">
-        <v>7060019</v>
+        <v>7060030</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1887,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515671</v>
+        <v>118515669</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,39 +1893,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585724</v>
+        <v>585726</v>
       </c>
       <c r="R13" t="n">
-        <v>7060051</v>
+        <v>7060027</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1994,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118515695</v>
+        <v>118515677</v>
       </c>
       <c r="B14" t="n">
-        <v>90500</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585636</v>
+        <v>585717</v>
       </c>
       <c r="R14" t="n">
-        <v>7060036</v>
+        <v>7060027</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2096,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118515696</v>
+        <v>118515682</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,39 +2097,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585601</v>
+        <v>585703</v>
       </c>
       <c r="R15" t="n">
-        <v>7060135</v>
+        <v>7060041</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2203,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118515693</v>
+        <v>118515694</v>
       </c>
       <c r="B16" t="n">
         <v>57290</v>
@@ -2237,21 +2217,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585653</v>
+        <v>585649</v>
       </c>
       <c r="R16" t="n">
-        <v>7060030</v>
+        <v>7060032</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2284,6 +2267,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färskt bohål, 20 cm djupt, 5cm i diameter, 1,5m ovan  mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118515682</v>
+        <v>118515673</v>
       </c>
       <c r="B17" t="n">
-        <v>90522</v>
+        <v>57443</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2326,34 +2314,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585703</v>
+        <v>585723</v>
       </c>
       <c r="R17" t="n">
-        <v>7060041</v>
+        <v>7060030</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515693</v>
+        <v>118515669</v>
       </c>
       <c r="B12" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,39 +1786,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585653</v>
+        <v>585726</v>
       </c>
       <c r="R12" t="n">
-        <v>7060030</v>
+        <v>7060027</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1877,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515669</v>
+        <v>118515693</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,34 +1888,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585726</v>
+        <v>585653</v>
       </c>
       <c r="R13" t="n">
-        <v>7060027</v>
+        <v>7060030</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118481566</v>
+        <v>118480755</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585607</v>
+        <v>585567</v>
       </c>
       <c r="R2" t="n">
-        <v>7060088</v>
+        <v>7060175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118480755</v>
+        <v>118481566</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -940,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585567</v>
+        <v>585607</v>
       </c>
       <c r="R4" t="n">
-        <v>7060175</v>
+        <v>7060088</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515676</v>
+        <v>118515673</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1154,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585719</v>
+        <v>585723</v>
       </c>
       <c r="R6" t="n">
-        <v>7060029</v>
+        <v>7060030</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1245,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515695</v>
+        <v>118515692</v>
       </c>
       <c r="B7" t="n">
-        <v>90500</v>
+        <v>90522</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585636</v>
+        <v>585656</v>
       </c>
       <c r="R7" t="n">
-        <v>7060036</v>
+        <v>7060035</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1347,7 +1354,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118515696</v>
+        <v>118515671</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1392,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585601</v>
+        <v>585724</v>
       </c>
       <c r="R8" t="n">
-        <v>7060135</v>
+        <v>7060051</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1454,7 +1461,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118515671</v>
+        <v>118515676</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1499,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585724</v>
+        <v>585719</v>
       </c>
       <c r="R9" t="n">
-        <v>7060051</v>
+        <v>7060029</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1561,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118515692</v>
+        <v>118515682</v>
       </c>
       <c r="B10" t="n">
         <v>90522</v>
@@ -1601,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585656</v>
+        <v>585703</v>
       </c>
       <c r="R10" t="n">
-        <v>7060035</v>
+        <v>7060041</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1663,7 +1670,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118515681</v>
+        <v>118515696</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1699,7 +1706,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1708,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585705</v>
+        <v>585601</v>
       </c>
       <c r="R11" t="n">
-        <v>7060019</v>
+        <v>7060135</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1770,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515669</v>
+        <v>118515693</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,34 +1793,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585726</v>
+        <v>585653</v>
       </c>
       <c r="R12" t="n">
-        <v>7060027</v>
+        <v>7060030</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1872,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515693</v>
+        <v>118515669</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,39 +1900,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585653</v>
+        <v>585726</v>
       </c>
       <c r="R13" t="n">
-        <v>7060030</v>
+        <v>7060027</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2081,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118515682</v>
+        <v>118515695</v>
       </c>
       <c r="B15" t="n">
-        <v>90522</v>
+        <v>90500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,21 +2104,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585703</v>
+        <v>585636</v>
       </c>
       <c r="R15" t="n">
-        <v>7060041</v>
+        <v>7060036</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2183,7 +2190,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118515694</v>
+        <v>118515681</v>
       </c>
       <c r="B16" t="n">
         <v>57290</v>
@@ -2217,24 +2224,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585649</v>
+        <v>585705</v>
       </c>
       <c r="R16" t="n">
-        <v>7060032</v>
+        <v>7060019</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2267,11 +2271,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färskt bohål, 20 cm djupt, 5cm i diameter, 1,5m ovan  mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118515673</v>
+        <v>118515694</v>
       </c>
       <c r="B17" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,33 +2313,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2350,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585723</v>
+        <v>585649</v>
       </c>
       <c r="R17" t="n">
-        <v>7060030</v>
+        <v>7060032</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2386,6 +2381,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färskt bohål, 20 cm djupt, 5cm i diameter, 1,5m ovan  mark</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118480755</v>
+        <v>118481566</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585567</v>
+        <v>585607</v>
       </c>
       <c r="R2" t="n">
-        <v>7060175</v>
+        <v>7060088</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118481712</v>
+        <v>118480755</v>
       </c>
       <c r="B3" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585629</v>
+        <v>585567</v>
       </c>
       <c r="R3" t="n">
-        <v>7060045</v>
+        <v>7060175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118481566</v>
+        <v>118481712</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585607</v>
+        <v>585629</v>
       </c>
       <c r="R4" t="n">
-        <v>7060088</v>
+        <v>7060045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515673</v>
+        <v>118515693</v>
       </c>
       <c r="B6" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,43 +1154,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585723</v>
+        <v>585653</v>
       </c>
       <c r="R6" t="n">
         <v>7060030</v>
@@ -1252,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515692</v>
+        <v>118515669</v>
       </c>
       <c r="B7" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585656</v>
+        <v>585726</v>
       </c>
       <c r="R7" t="n">
-        <v>7060035</v>
+        <v>7060027</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1354,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118515671</v>
+        <v>118515692</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,39 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585724</v>
+        <v>585656</v>
       </c>
       <c r="R8" t="n">
-        <v>7060051</v>
+        <v>7060035</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1461,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118515676</v>
+        <v>118515677</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,39 +1465,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585719</v>
+        <v>585717</v>
       </c>
       <c r="R9" t="n">
-        <v>7060029</v>
+        <v>7060027</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1568,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118515682</v>
+        <v>118515695</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
+        <v>90507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585703</v>
+        <v>585636</v>
       </c>
       <c r="R10" t="n">
-        <v>7060041</v>
+        <v>7060036</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1670,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118515696</v>
+        <v>118515681</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1706,7 +1689,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1715,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585601</v>
+        <v>585705</v>
       </c>
       <c r="R11" t="n">
-        <v>7060135</v>
+        <v>7060019</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1777,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515693</v>
+        <v>118515696</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1822,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585653</v>
+        <v>585601</v>
       </c>
       <c r="R12" t="n">
-        <v>7060030</v>
+        <v>7060135</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1884,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515669</v>
+        <v>118515682</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1924,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585726</v>
+        <v>585703</v>
       </c>
       <c r="R13" t="n">
-        <v>7060027</v>
+        <v>7060041</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1986,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118515677</v>
+        <v>118515676</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,34 +1985,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585717</v>
+        <v>585719</v>
       </c>
       <c r="R14" t="n">
-        <v>7060027</v>
+        <v>7060029</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2088,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118515695</v>
+        <v>118515671</v>
       </c>
       <c r="B15" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2104,34 +2092,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585636</v>
+        <v>585724</v>
       </c>
       <c r="R15" t="n">
-        <v>7060036</v>
+        <v>7060051</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2190,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118515681</v>
+        <v>118515694</v>
       </c>
       <c r="B16" t="n">
         <v>57290</v>
@@ -2224,21 +2217,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585705</v>
+        <v>585649</v>
       </c>
       <c r="R16" t="n">
-        <v>7060019</v>
+        <v>7060032</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2271,6 +2267,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färskt bohål, 20 cm djupt, 5cm i diameter, 1,5m ovan  mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118515694</v>
+        <v>118515673</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>57443</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,29 +2314,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2345,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585649</v>
+        <v>585723</v>
       </c>
       <c r="R17" t="n">
-        <v>7060032</v>
+        <v>7060030</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2381,11 +2386,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färskt bohål, 20 cm djupt, 5cm i diameter, 1,5m ovan  mark</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118480755</v>
+        <v>118481712</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585567</v>
+        <v>585629</v>
       </c>
       <c r="R3" t="n">
-        <v>7060175</v>
+        <v>7060045</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118481712</v>
+        <v>118481860</v>
       </c>
       <c r="B4" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585629</v>
+        <v>585632</v>
       </c>
       <c r="R4" t="n">
-        <v>7060045</v>
+        <v>7060018</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118481860</v>
+        <v>118480755</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1057,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585632</v>
+        <v>585567</v>
       </c>
       <c r="R5" t="n">
-        <v>7060018</v>
+        <v>7060175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515693</v>
+        <v>118515671</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585653</v>
+        <v>585724</v>
       </c>
       <c r="R6" t="n">
-        <v>7060030</v>
+        <v>7060051</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515669</v>
+        <v>118515682</v>
       </c>
       <c r="B7" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585726</v>
+        <v>585703</v>
       </c>
       <c r="R7" t="n">
-        <v>7060027</v>
+        <v>7060041</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118515692</v>
+        <v>118515673</v>
       </c>
       <c r="B8" t="n">
-        <v>90529</v>
+        <v>57443</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1363,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585656</v>
+        <v>585723</v>
       </c>
       <c r="R8" t="n">
-        <v>7060035</v>
+        <v>7060030</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1449,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118515677</v>
+        <v>118515676</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,34 +1477,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585717</v>
+        <v>585719</v>
       </c>
       <c r="R9" t="n">
-        <v>7060027</v>
+        <v>7060029</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1551,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118515695</v>
+        <v>118515681</v>
       </c>
       <c r="B10" t="n">
-        <v>90507</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,34 +1584,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585636</v>
+        <v>585705</v>
       </c>
       <c r="R10" t="n">
-        <v>7060036</v>
+        <v>7060019</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1653,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118515681</v>
+        <v>118515669</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,39 +1691,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585705</v>
+        <v>585726</v>
       </c>
       <c r="R11" t="n">
-        <v>7060019</v>
+        <v>7060027</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1760,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515696</v>
+        <v>118515692</v>
       </c>
       <c r="B12" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,39 +1793,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585601</v>
+        <v>585656</v>
       </c>
       <c r="R12" t="n">
-        <v>7060135</v>
+        <v>7060035</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1867,10 +1879,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515682</v>
+        <v>118515696</v>
       </c>
       <c r="B13" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,34 +1895,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585703</v>
+        <v>585601</v>
       </c>
       <c r="R13" t="n">
-        <v>7060041</v>
+        <v>7060135</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1969,7 +1986,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118515676</v>
+        <v>118515694</v>
       </c>
       <c r="B14" t="n">
         <v>57290</v>
@@ -2003,21 +2020,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585719</v>
+        <v>585649</v>
       </c>
       <c r="R14" t="n">
-        <v>7060029</v>
+        <v>7060032</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2050,6 +2070,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färskt bohål, 20 cm djupt, 5cm i diameter, 1,5m ovan  mark</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,7 +2101,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118515671</v>
+        <v>118515693</v>
       </c>
       <c r="B15" t="n">
         <v>57290</v>
@@ -2121,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585724</v>
+        <v>585653</v>
       </c>
       <c r="R15" t="n">
-        <v>7060051</v>
+        <v>7060030</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2183,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118515694</v>
+        <v>118515677</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,42 +2224,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585649</v>
+        <v>585717</v>
       </c>
       <c r="R16" t="n">
-        <v>7060032</v>
+        <v>7060027</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2267,11 +2284,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färskt bohål, 20 cm djupt, 5cm i diameter, 1,5m ovan  mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118515673</v>
+        <v>118515695</v>
       </c>
       <c r="B17" t="n">
-        <v>57443</v>
+        <v>90507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,46 +2326,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585723</v>
+        <v>585636</v>
       </c>
       <c r="R17" t="n">
-        <v>7060030</v>
+        <v>7060036</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -1363,7 +1363,7 @@
         <v>118515693</v>
       </c>
       <c r="B8" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,11 +1394,14 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
@@ -1441,6 +1444,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Både färska och äldre ringhack, gran. Bilder från återbesök feb 2025.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122758926</v>
+        <v>122758910</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585628</v>
+        <v>585667</v>
       </c>
       <c r="R18" t="n">
-        <v>7060081</v>
+        <v>7060060</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2542,7 +2542,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122758910</v>
+        <v>122759628</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2578,7 +2578,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585667</v>
+        <v>585623</v>
       </c>
       <c r="R19" t="n">
-        <v>7060060</v>
+        <v>7060128</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,24 +2620,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,19 +2642,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122759628</v>
+        <v>122758926</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2700,7 +2690,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2709,13 +2699,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585623</v>
+        <v>585628</v>
       </c>
       <c r="R20" t="n">
-        <v>7060128</v>
+        <v>7060081</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2742,14 +2732,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,12 +2764,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122758910</v>
+        <v>122759628</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2456,7 +2456,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585667</v>
+        <v>585623</v>
       </c>
       <c r="R18" t="n">
-        <v>7060060</v>
+        <v>7060128</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,24 +2498,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,19 +2520,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122759628</v>
+        <v>122758926</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2578,7 +2568,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2587,13 +2577,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585623</v>
+        <v>585628</v>
       </c>
       <c r="R19" t="n">
-        <v>7060128</v>
+        <v>7060081</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,14 +2610,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2642,19 +2642,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122758926</v>
+        <v>122758910</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585628</v>
+        <v>585667</v>
       </c>
       <c r="R20" t="n">
-        <v>7060081</v>
+        <v>7060060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122759628</v>
+        <v>122758910</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2456,7 +2456,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585623</v>
+        <v>585667</v>
       </c>
       <c r="R18" t="n">
-        <v>7060128</v>
+        <v>7060060</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,14 +2498,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,19 +2530,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122758926</v>
+        <v>122759628</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2568,7 +2578,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2577,13 +2587,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585628</v>
+        <v>585623</v>
       </c>
       <c r="R19" t="n">
-        <v>7060081</v>
+        <v>7060128</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,24 +2620,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2642,19 +2642,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122758910</v>
+        <v>122758926</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585667</v>
+        <v>585628</v>
       </c>
       <c r="R20" t="n">
-        <v>7060060</v>
+        <v>7060081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122758910</v>
+        <v>122758926</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585667</v>
+        <v>585628</v>
       </c>
       <c r="R18" t="n">
-        <v>7060060</v>
+        <v>7060081</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2654,7 +2654,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122758926</v>
+        <v>122758910</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585628</v>
+        <v>585667</v>
       </c>
       <c r="R20" t="n">
-        <v>7060081</v>
+        <v>7060060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122758926</v>
+        <v>122759628</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2456,7 +2456,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585628</v>
+        <v>585623</v>
       </c>
       <c r="R18" t="n">
-        <v>7060081</v>
+        <v>7060128</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,24 +2498,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,19 +2520,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122759628</v>
+        <v>122758910</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2578,7 +2568,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2587,13 +2577,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585623</v>
+        <v>585667</v>
       </c>
       <c r="R19" t="n">
-        <v>7060128</v>
+        <v>7060060</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,14 +2610,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2642,19 +2642,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122758910</v>
+        <v>122758926</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585667</v>
+        <v>585628</v>
       </c>
       <c r="R20" t="n">
-        <v>7060060</v>
+        <v>7060081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122759628</v>
+        <v>122758910</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2456,7 +2456,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585623</v>
+        <v>585667</v>
       </c>
       <c r="R18" t="n">
-        <v>7060128</v>
+        <v>7060060</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,14 +2498,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,19 +2530,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122758910</v>
+        <v>122758926</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2577,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585667</v>
+        <v>585628</v>
       </c>
       <c r="R19" t="n">
-        <v>7060060</v>
+        <v>7060081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,7 +2622,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2622,7 +2632,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2654,7 +2664,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122758926</v>
+        <v>122759628</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2690,7 +2700,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2699,13 +2709,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585628</v>
+        <v>585623</v>
       </c>
       <c r="R20" t="n">
-        <v>7060081</v>
+        <v>7060128</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,24 +2742,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,12 +2764,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -1248,7 +1248,7 @@
         <v>118515694</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>118515693</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122758910</v>
+        <v>122759628</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585667</v>
+        <v>585623</v>
       </c>
       <c r="R18" t="n">
-        <v>7060060</v>
+        <v>7060128</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,24 +2498,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,22 +2520,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122758926</v>
+        <v>122758910</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,10 +2577,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585628</v>
+        <v>585667</v>
       </c>
       <c r="R19" t="n">
-        <v>7060081</v>
+        <v>7060060</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2622,7 +2612,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2632,7 +2622,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2664,10 +2654,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122759628</v>
+        <v>122758926</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2700,7 +2690,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2709,13 +2699,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585623</v>
+        <v>585628</v>
       </c>
       <c r="R20" t="n">
-        <v>7060128</v>
+        <v>7060081</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2742,14 +2732,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,12 +2764,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122759628</v>
+        <v>122758926</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2456,7 +2456,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585623</v>
+        <v>585628</v>
       </c>
       <c r="R18" t="n">
-        <v>7060128</v>
+        <v>7060081</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,14 +2498,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,12 +2530,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2654,7 +2664,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122758926</v>
+        <v>122759628</v>
       </c>
       <c r="B20" t="n">
         <v>57481</v>
@@ -2690,7 +2700,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2699,13 +2709,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585628</v>
+        <v>585623</v>
       </c>
       <c r="R20" t="n">
-        <v>7060081</v>
+        <v>7060128</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,24 +2742,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,12 +2764,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2774,6 +2774,332 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125264538</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>585625</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7060059</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125263786</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>585641</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7060037</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125264243</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>585672</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7060034</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2776,7 +2776,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125264538</v>
+        <v>125263786</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2812,7 +2812,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585625</v>
+        <v>585641</v>
       </c>
       <c r="R21" t="n">
-        <v>7060059</v>
+        <v>7060037</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125263786</v>
+        <v>125264243</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,39 +2904,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585641</v>
+        <v>585672</v>
       </c>
       <c r="R22" t="n">
-        <v>7060037</v>
+        <v>7060034</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2969,11 +2964,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,10 +2990,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125264243</v>
+        <v>125264538</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,34 +3006,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585672</v>
+        <v>585625</v>
       </c>
       <c r="R23" t="n">
-        <v>7060034</v>
+        <v>7060059</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3076,6 +3071,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2776,10 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125263786</v>
+        <v>125264243</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,39 +2792,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585641</v>
+        <v>585672</v>
       </c>
       <c r="R21" t="n">
-        <v>7060037</v>
+        <v>7060034</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2857,11 +2852,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125264243</v>
+        <v>125263786</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,34 +2894,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585672</v>
+        <v>585641</v>
       </c>
       <c r="R22" t="n">
-        <v>7060034</v>
+        <v>7060037</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2964,6 +2959,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2776,10 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125264243</v>
+        <v>125264538</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,34 +2792,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585672</v>
+        <v>585625</v>
       </c>
       <c r="R21" t="n">
-        <v>7060034</v>
+        <v>7060059</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2852,6 +2857,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2878,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125263786</v>
+        <v>125264243</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,39 +2904,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585641</v>
+        <v>585672</v>
       </c>
       <c r="R22" t="n">
-        <v>7060037</v>
+        <v>7060034</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2959,11 +2964,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,7 +2990,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125264538</v>
+        <v>125263786</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3026,7 +3026,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585625</v>
+        <v>585641</v>
       </c>
       <c r="R23" t="n">
-        <v>7060059</v>
+        <v>7060037</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125264243</v>
+        <v>125263786</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,34 +2904,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585672</v>
+        <v>585641</v>
       </c>
       <c r="R22" t="n">
-        <v>7060034</v>
+        <v>7060037</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2964,6 +2969,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,10 +3000,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125263786</v>
+        <v>125264243</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3006,39 +3016,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585641</v>
+        <v>585672</v>
       </c>
       <c r="R23" t="n">
-        <v>7060037</v>
+        <v>7060034</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3071,11 +3076,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125263786</v>
+        <v>125264243</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,39 +2904,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585641</v>
+        <v>585672</v>
       </c>
       <c r="R22" t="n">
-        <v>7060037</v>
+        <v>7060034</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2969,11 +2964,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,10 +2990,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125264243</v>
+        <v>125263786</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,34 +3006,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585672</v>
+        <v>585641</v>
       </c>
       <c r="R23" t="n">
-        <v>7060034</v>
+        <v>7060037</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3076,6 +3071,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2776,10 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125264538</v>
+        <v>125263786</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585625</v>
+        <v>585641</v>
       </c>
       <c r="R21" t="n">
-        <v>7060059</v>
+        <v>7060037</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125264243</v>
+        <v>125264538</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,34 +2904,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585672</v>
+        <v>585625</v>
       </c>
       <c r="R22" t="n">
-        <v>7060034</v>
+        <v>7060059</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2964,6 +2969,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,10 +3000,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125263786</v>
+        <v>125264243</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3006,39 +3016,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585641</v>
+        <v>585672</v>
       </c>
       <c r="R23" t="n">
-        <v>7060037</v>
+        <v>7060034</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3071,11 +3076,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2776,7 +2776,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125263786</v>
+        <v>125264538</v>
       </c>
       <c r="B21" t="n">
         <v>57635</v>
@@ -2812,7 +2812,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585641</v>
+        <v>585625</v>
       </c>
       <c r="R21" t="n">
-        <v>7060037</v>
+        <v>7060059</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125264538</v>
+        <v>125264243</v>
       </c>
       <c r="B22" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2904,39 +2904,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585625</v>
+        <v>585672</v>
       </c>
       <c r="R22" t="n">
-        <v>7060059</v>
+        <v>7060034</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2969,11 +2964,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,10 +2990,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125264243</v>
+        <v>125263786</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,34 +3006,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585672</v>
+        <v>585641</v>
       </c>
       <c r="R23" t="n">
-        <v>7060034</v>
+        <v>7060037</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3076,6 +3071,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2776,15 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125264538</v>
+        <v>125264243</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,39 +2787,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585625</v>
+        <v>585672</v>
       </c>
       <c r="R21" t="n">
-        <v>7060059</v>
+        <v>7060034</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2857,11 +2847,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,15 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125264243</v>
+        <v>125263786</v>
       </c>
       <c r="B22" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,34 +2884,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585672</v>
+        <v>585641</v>
       </c>
       <c r="R22" t="n">
-        <v>7060034</v>
+        <v>7060037</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2964,6 +2949,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,15 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125263786</v>
+        <v>125264538</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3011,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3035,10 +3020,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585641</v>
+        <v>585625</v>
       </c>
       <c r="R23" t="n">
-        <v>7060037</v>
+        <v>7060059</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3075,7 +3060,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2779,7 +2779,7 @@
         <v>125264243</v>
       </c>
       <c r="B21" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 33209-2020 artfynd.xlsx
+++ b/artfynd/A 33209-2020 artfynd.xlsx
@@ -2779,7 +2779,7 @@
         <v>125264243</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
